--- a/data/trans_orig/P13A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según días que sufre dolor de cabeza al mes en 2023</t>
+          <t>Población según cuántos días al mes sufre dolor de cabeza en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22847</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>23760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45041</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63849</t>
+          <t>63978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98166</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98173</t>
+          <t>98012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129995</t>
+          <t>129072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>172395</t>
+          <t>170659</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>217872</t>
+          <t>216527</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>383943</t>
+          <t>384177</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>420797</t>
+          <t>421639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>283279</t>
+          <t>285511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>318990</t>
+          <t>318934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>681522</t>
+          <t>681336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>729856</t>
+          <t>730023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28598</t>
+          <t>28154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36388</t>
+          <t>36901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59755</t>
+          <t>60465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93738</t>
+          <t>95307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86591</t>
+          <t>87815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116962</t>
+          <t>117235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156611</t>
+          <t>157418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>202176</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>349806</t>
+          <t>346305</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>384292</t>
+          <t>382921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>232749</t>
+          <t>230274</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>264538</t>
+          <t>262472</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>590462</t>
+          <t>591930</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>638880</t>
+          <t>639131</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34580</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>23431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7548</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36879</t>
+          <t>36627</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26210</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119122</t>
+          <t>122320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33977</t>
+          <t>34554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52925</t>
+          <t>52339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46968</t>
+          <t>49627</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170181</t>
+          <t>170036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>515028</t>
+          <t>512566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>634163</t>
+          <t>633306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89410</t>
+          <t>90605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109981</t>
+          <t>110364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>602837</t>
+          <t>603919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>767511</t>
+          <t>765654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55326</t>
+          <t>54418</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35254</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67208</t>
+          <t>66609</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43437</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,47 +2565,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>41022</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>19278</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>58075</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>41022</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>19046</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>57273</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48932</t>
+          <t>50072</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91701</t>
+          <t>90644</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>159079</t>
+          <t>162640</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>219810</t>
+          <t>222533</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>260192</t>
+          <t>262146</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>679797</t>
+          <t>702629</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>434918</t>
+          <t>433133</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1020752</t>
+          <t>1027336</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>768117</t>
+          <t>764660</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>830970</t>
+          <t>827448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,17 +2806,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>476968</t>
+          <t>476969</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255802</t>
+          <t>237113</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>613910</t>
+          <t>611924</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>895823</t>
+          <t>887766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1437393</t>
+          <t>1438306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>975441</t>
+          <t>975442</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>975441</t>
+          <t>975442</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>975441</t>
+          <t>975442</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37600</t>
+          <t>38146</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73904</t>
+          <t>75221</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49134</t>
+          <t>49013</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85315</t>
+          <t>88268</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37772</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66169</t>
+          <t>66792</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49535</t>
+          <t>49830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78186</t>
+          <t>78133</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75421</t>
+          <t>74085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113274</t>
+          <t>114033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>207238</t>
+          <t>206229</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>413084</t>
+          <t>416987</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>295102</t>
+          <t>298748</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>523186</t>
+          <t>541121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>336614</t>
+          <t>336971</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>379036</t>
+          <t>378159</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>347170</t>
+          <t>341017</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>516898</t>
+          <t>518353</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>677789</t>
+          <t>664061</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>882450</t>
+          <t>878778</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24524</t>
+          <t>23973</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28187</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29064</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>50806</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>57794</t>
+          <t>58241</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38278</t>
+          <t>39024</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>149837</t>
+          <t>152388</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>194120</t>
+          <t>195082</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>169958</t>
+          <t>168732</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>223514</t>
+          <t>222053</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>194665</t>
+          <t>192729</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>224486</t>
+          <t>222962</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>507228</t>
+          <t>506599</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>553492</t>
+          <t>551413</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>710387</t>
+          <t>710579</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>770751</t>
+          <t>770245</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>51906</t>
+          <t>52623</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>118846</t>
+          <t>117361</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>175979</t>
+          <t>174713</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>154432</t>
+          <t>154684</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>217144</t>
+          <t>217310</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>59599</t>
+          <t>58150</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>100676</t>
+          <t>100607</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>148476</t>
+          <t>144311</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>207232</t>
+          <t>208976</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>224350</t>
+          <t>221384</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>295817</t>
+          <t>294077</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>405376</t>
+          <t>410214</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>589362</t>
+          <t>588831</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>923467</t>
+          <t>929931</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1568548</t>
+          <t>1629758</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1419764</t>
+          <t>1409632</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2216838</t>
+          <t>2214696</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2649048</t>
+          <t>2648499</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2857709</t>
+          <t>2862823</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1722079</t>
+          <t>1676855</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2286444</t>
+          <t>2279763</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4349760</t>
+          <t>4358098</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5080737</t>
+          <t>5085920</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>24020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9550</t>
+          <t>11790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23760</t>
+          <t>28029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>15918</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>29112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>34029</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24701</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>47446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>90886</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63978</t>
+          <t>74363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99795</t>
+          <t>112172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>113611</t>
+          <t>121375</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98012</t>
+          <t>104645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129072</t>
+          <t>138185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>194090</t>
+          <t>212261</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170659</t>
+          <t>187566</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>216527</t>
+          <t>238890</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>404295</t>
+          <t>438380</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>384177</t>
+          <t>416827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>421639</t>
+          <t>457008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>302762</t>
+          <t>330893</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>285511</t>
+          <t>313465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>318934</t>
+          <t>349786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>707057</t>
+          <t>769273</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>681336</t>
+          <t>739192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>730023</t>
+          <t>794108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>502386</t>
+          <t>547693</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>502386</t>
+          <t>547693</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502386</t>
+          <t>547693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>446752</t>
+          <t>485375</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446752</t>
+          <t>485375</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446752</t>
+          <t>485375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>949138</t>
+          <t>1033068</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>949138</t>
+          <t>1033068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>949138</t>
+          <t>1033068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17901</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19953</t>
+          <t>22696</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>31871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>29064</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18497</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36901</t>
+          <t>40080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75605</t>
+          <t>79881</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60465</t>
+          <t>63578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95307</t>
+          <t>98577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102153</t>
+          <t>110165</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87815</t>
+          <t>95068</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117235</t>
+          <t>127742</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>177758</t>
+          <t>190047</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157418</t>
+          <t>167376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202176</t>
+          <t>215137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>367684</t>
+          <t>393875</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>346305</t>
+          <t>375169</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>382921</t>
+          <t>410728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>247874</t>
+          <t>277164</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>230274</t>
+          <t>259765</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>262472</t>
+          <t>294111</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>615558</t>
+          <t>671039</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>591930</t>
+          <t>643774</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>639131</t>
+          <t>695931</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>450389</t>
+          <t>481151</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>450389</t>
+          <t>481151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>450389</t>
+          <t>481151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>381779</t>
+          <t>422282</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>381779</t>
+          <t>422282</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381779</t>
+          <t>422282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>832168</t>
+          <t>903433</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>832168</t>
+          <t>903433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>832168</t>
+          <t>903433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>24170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33433</t>
+          <t>34053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23431</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,22 +2011,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>22609</t>
+          <t>26871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36627</t>
+          <t>38890</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>71759</t>
+          <t>80224</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>62250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122320</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43153</t>
+          <t>49621</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>40516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52339</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>114912</t>
+          <t>129845</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49627</t>
+          <t>109132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170036</t>
+          <t>151352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>575684</t>
+          <t>368060</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>512566</t>
+          <t>346916</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>633306</t>
+          <t>387630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>100072</t>
+          <t>111345</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90605</t>
+          <t>100466</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110364</t>
+          <t>122991</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>675755</t>
+          <t>479405</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>603919</t>
+          <t>453722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>765654</t>
+          <t>502539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>76,41%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>833772</t>
+          <t>657675</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>833772</t>
+          <t>657675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>833772</t>
+          <t>657675</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>45345</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54418</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>51875</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>45819</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66609</t>
+          <t>74611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31547</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>23527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44325</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>41022</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58075</t>
+          <t>54928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>72569</t>
+          <t>76655</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50072</t>
+          <t>62552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>90644</t>
+          <t>96050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>187259</t>
+          <t>196513</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162640</t>
+          <t>169839</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>222533</t>
+          <t>224796</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>418315</t>
+          <t>236382</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>262146</t>
+          <t>214740</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>702629</t>
+          <t>260526</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>605574</t>
+          <t>432895</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>433133</t>
+          <t>398007</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1027336</t>
+          <t>470185</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>800775</t>
+          <t>883846</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>764660</t>
+          <t>854038</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>827448</t>
+          <t>913727</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>476969</t>
+          <t>534202</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>237113</t>
+          <t>507138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>611924</t>
+          <t>557797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1277743</t>
+          <t>1418048</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>887766</t>
+          <t>1375166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1438306</t>
+          <t>1456616</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1032320</t>
+          <t>1127861</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1032320</t>
+          <t>1127861</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1032320</t>
+          <t>1127861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>975442</t>
+          <t>858360</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>975442</t>
+          <t>858360</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>975442</t>
+          <t>858360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2007761</t>
+          <t>1986220</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2007761</t>
+          <t>1986220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2007761</t>
+          <t>1986220</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>53863</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38146</t>
+          <t>44700</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75221</t>
+          <t>71592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>67614</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49013</t>
+          <t>54272</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>88268</t>
+          <t>83553</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>20187</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>53785</t>
+          <t>58393</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>47209</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66792</t>
+          <t>69825</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>63711</t>
+          <t>70929</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49830</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78133</t>
+          <t>83595</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>92182</t>
+          <t>104519</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74085</t>
+          <t>84278</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114033</t>
+          <t>125555</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>268246</t>
+          <t>218831</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>206229</t>
+          <t>198317</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>416987</t>
+          <t>241717</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>360428</t>
+          <t>323350</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>298748</t>
+          <t>292325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>541121</t>
+          <t>352679</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>359661</t>
+          <t>436519</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>336971</t>
+          <t>415474</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>378159</t>
+          <t>458627</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>460966</t>
+          <t>492578</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>341017</t>
+          <t>468670</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>518353</t>
+          <t>514631</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>820627</t>
+          <t>929097</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>664061</t>
+          <t>894978</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>878778</t>
+          <t>960965</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>472599</t>
+          <t>565442</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>472599</t>
+          <t>565442</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>472599</t>
+          <t>565442</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>836860</t>
+          <t>825548</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>836860</t>
+          <t>825548</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>836860</t>
+          <t>825548</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1309459</t>
+          <t>1390990</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1309459</t>
+          <t>1390990</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1309459</t>
+          <t>1390990</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,22 +3570,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23973</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>29911</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19590</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>42669</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28926</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50806</t>
+          <t>56929</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,17 +3753,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>43091</t>
+          <t>46590</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>34064</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>58241</t>
+          <t>62475</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39024</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>172866</t>
+          <t>183499</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>152388</t>
+          <t>160620</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>195082</t>
+          <t>206873</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>193661</t>
+          <t>206140</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>168732</t>
+          <t>180594</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>222053</t>
+          <t>232191</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>212506</t>
+          <t>207613</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>192729</t>
+          <t>189551</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>222962</t>
+          <t>218424</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>529660</t>
+          <t>596654</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>506599</t>
+          <t>570962</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>551413</t>
+          <t>622752</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>742166</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>710579</t>
+          <t>774730</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>770245</t>
+          <t>832133</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>757988</t>
+          <t>840861</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>757988</t>
+          <t>840861</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>757988</t>
+          <t>840861</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>998495</t>
+          <t>1078089</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>998495</t>
+          <t>1078089</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>998495</t>
+          <t>1078089</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>52623</t>
+          <t>54418</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>147311</t>
+          <t>159764</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>117361</t>
+          <t>138639</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>174713</t>
+          <t>181004</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>184705</t>
+          <t>199672</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>174800</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>217310</t>
+          <t>226067</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>79552</t>
+          <t>87258</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>58150</t>
+          <t>69815</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>100607</t>
+          <t>109415</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>181207</t>
+          <t>196879</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>144311</t>
+          <t>174107</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>208976</t>
+          <t>221171</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>260759</t>
+          <t>284137</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>221384</t>
+          <t>251376</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>294077</t>
+          <t>313299</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>528079</t>
+          <t>574662</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>410214</t>
+          <t>528410</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>588831</t>
+          <t>627397</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1118345</t>
+          <t>919874</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>929931</t>
+          <t>877024</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1629758</t>
+          <t>968086</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1646423</t>
+          <t>1494536</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1409632</t>
+          <t>1426660</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2214696</t>
+          <t>1559667</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2720604</t>
+          <t>2728292</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2648499</t>
+          <t>2674713</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2862823</t>
+          <t>2777488</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2118302</t>
+          <t>2342837</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1676855</t>
+          <t>2292675</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2279763</t>
+          <t>2392752</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4838906</t>
+          <t>5071130</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4358098</t>
+          <t>4994044</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5085920</t>
+          <t>5143772</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3365628</t>
+          <t>3430121</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3365628</t>
+          <t>3430121</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3365628</t>
+          <t>3430121</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3565165</t>
+          <t>3619355</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3565165</t>
+          <t>3619355</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3565165</t>
+          <t>3619355</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6930793</t>
+          <t>7049476</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6930793</t>
+          <t>7049476</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6930793</t>
+          <t>7049476</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
